--- a/carddata/Duel_Masters_Card_Database.xlsx
+++ b/carddata/Duel_Masters_Card_Database.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2434">
   <si>
     <t>Name</t>
   </si>
@@ -7177,10 +7177,142 @@
     <t>Zetsu Gowan, Savage Faerie</t>
   </si>
   <si>
-    <t>Card_Back_no_logo</t>
-  </si>
-  <si>
-    <t>card back</t>
+    <t>Aqua Grappler</t>
+  </si>
+  <si>
+    <t>Aqua Ranger</t>
+  </si>
+  <si>
+    <t>Bakkra Horn, the Silent</t>
+  </si>
+  <si>
+    <t>Bruiser Dragon</t>
+  </si>
+  <si>
+    <t>Candy Cluster</t>
+  </si>
+  <si>
+    <t>Carbonite Scarab</t>
+  </si>
+  <si>
+    <t>Coliseum Shell</t>
+  </si>
+  <si>
+    <t>Corpse Charger</t>
+  </si>
+  <si>
+    <t>Dimension Splitter</t>
+  </si>
+  <si>
+    <t>Dracobarrier</t>
+  </si>
+  <si>
+    <t>Dracodance Totem</t>
+  </si>
+  <si>
+    <t>Emperor Quazla</t>
+  </si>
+  <si>
+    <t>Evolution Creature</t>
+  </si>
+  <si>
+    <t>Eureka Charger</t>
+  </si>
+  <si>
+    <t>Furious Onslaught</t>
+  </si>
+  <si>
+    <t>Gachack, Mechanical Doll</t>
+  </si>
+  <si>
+    <t>Gigaclaws</t>
+  </si>
+  <si>
+    <t>Grape Globbo</t>
+  </si>
+  <si>
+    <t>Illusion fish</t>
+  </si>
+  <si>
+    <t>Kachua, Keeper of the Icegate</t>
+  </si>
+  <si>
+    <t>Kuukai, Finder of Karma</t>
+  </si>
+  <si>
+    <t>Kyrstron, Lair Delver</t>
+  </si>
+  <si>
+    <t>Lalicious</t>
+  </si>
+  <si>
+    <t>Lunar Charger</t>
+  </si>
+  <si>
+    <t>Magmadragon Jagalzor</t>
+  </si>
+  <si>
+    <t>Magmadragon Melgars</t>
+  </si>
+  <si>
+    <t>Nariel, the Oracle</t>
+  </si>
+  <si>
+    <t>Migalo, Vizier of Spycraft</t>
+  </si>
+  <si>
+    <t>Motorcycle Mutant</t>
+  </si>
+  <si>
+    <t>Muscle Charger</t>
+  </si>
+  <si>
+    <t>Nastasha, Channeler of Suns</t>
+  </si>
+  <si>
+    <t>Necrodragon Galbazeek</t>
+  </si>
+  <si>
+    <t>Necrodragon Giland</t>
+  </si>
+  <si>
+    <t>Prowling Elephish</t>
+  </si>
+  <si>
+    <t>Sasha, Channeler of Suns</t>
+  </si>
+  <si>
+    <t>Senia, Orchard Avenger</t>
+  </si>
+  <si>
+    <t>Slaphappy Soldier Galback</t>
+  </si>
+  <si>
+    <t>Sol Galla, Halo Guardian</t>
+  </si>
+  <si>
+    <t>Super Terradragon Bailas Gall</t>
+  </si>
+  <si>
+    <t>Thrumiss, Zephyr Guardian</t>
+  </si>
+  <si>
+    <t>Torpedo Skyterror</t>
+  </si>
+  <si>
+    <t>Totto Pipicchi</t>
+  </si>
+  <si>
+    <t>Tyrant Worm</t>
+  </si>
+  <si>
+    <t>Überdragon Bajula</t>
+  </si>
+  <si>
+    <t>Volcano Charger</t>
+  </si>
+  <si>
+    <t>Wave Lance</t>
   </si>
 </sst>
 </file>
@@ -8348,7 +8480,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E2549"/>
+  <dimension ref="A1:E2609"/>
   <sheetFormatPr defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="42" style="1" customWidth="1"/>
@@ -49772,7 +49904,7 @@
         <v>2324</v>
       </c>
       <c r="C2487" s="4">
-        <v>67</v>
+        <v>7</v>
       </c>
       <c r="D2487" s="5"/>
       <c r="E2487" t="s" s="3">
@@ -50252,7 +50384,7 @@
         <v>2324</v>
       </c>
       <c r="C2517" s="4">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="D2517" t="s" s="3">
         <v>7</v>
@@ -50783,17 +50915,1029 @@
       </c>
     </row>
     <row r="2549" ht="13.55" customHeight="1">
-      <c r="A2549" t="s" s="3">
+      <c r="A2549" s="5"/>
+      <c r="B2549" s="5"/>
+      <c r="C2549" s="5"/>
+      <c r="D2549" s="5"/>
+      <c r="E2549" s="5"/>
+    </row>
+    <row r="2550" ht="13.55" customHeight="1">
+      <c r="A2550" t="s" s="3">
         <v>2388</v>
       </c>
-      <c r="B2549" t="s" s="3">
+      <c r="B2550" t="s" s="3">
+        <v>547</v>
+      </c>
+      <c r="C2550" s="4">
+        <v>5</v>
+      </c>
+      <c r="D2550" t="s" s="3">
+        <v>7</v>
+      </c>
+      <c r="E2550" t="s" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2551" ht="13.55" customHeight="1">
+      <c r="A2551" t="s" s="3">
         <v>2389</v>
       </c>
-      <c r="C2549" s="5"/>
-      <c r="D2549" t="s" s="3">
-        <v>7</v>
-      </c>
-      <c r="E2549" t="s" s="3">
+      <c r="B2551" t="s" s="3">
+        <v>547</v>
+      </c>
+      <c r="C2551" s="4">
+        <v>6</v>
+      </c>
+      <c r="D2551" t="s" s="3">
+        <v>7</v>
+      </c>
+      <c r="E2551" t="s" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2552" ht="13.55" customHeight="1">
+      <c r="A2552" t="s" s="3">
+        <v>2390</v>
+      </c>
+      <c r="B2552" t="s" s="3">
+        <v>547</v>
+      </c>
+      <c r="C2552" s="4">
+        <v>4</v>
+      </c>
+      <c r="D2552" t="s" s="3">
+        <v>7</v>
+      </c>
+      <c r="E2552" t="s" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2553" ht="13.55" customHeight="1">
+      <c r="A2553" t="s" s="3">
+        <v>2391</v>
+      </c>
+      <c r="B2553" t="s" s="3">
+        <v>547</v>
+      </c>
+      <c r="C2553" s="4">
+        <v>5</v>
+      </c>
+      <c r="D2553" t="s" s="3">
+        <v>7</v>
+      </c>
+      <c r="E2553" t="s" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2554" ht="13.55" customHeight="1">
+      <c r="A2554" t="s" s="3">
+        <v>2392</v>
+      </c>
+      <c r="B2554" t="s" s="3">
+        <v>547</v>
+      </c>
+      <c r="C2554" s="4">
+        <v>3</v>
+      </c>
+      <c r="D2554" t="s" s="3">
+        <v>7</v>
+      </c>
+      <c r="E2554" t="s" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2555" ht="13.55" customHeight="1">
+      <c r="A2555" t="s" s="3">
+        <v>2393</v>
+      </c>
+      <c r="B2555" t="s" s="3">
+        <v>547</v>
+      </c>
+      <c r="C2555" s="4">
+        <v>4</v>
+      </c>
+      <c r="D2555" t="s" s="3">
+        <v>7</v>
+      </c>
+      <c r="E2555" t="s" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2556" ht="13.55" customHeight="1">
+      <c r="A2556" t="s" s="3">
+        <v>2394</v>
+      </c>
+      <c r="B2556" t="s" s="3">
+        <v>547</v>
+      </c>
+      <c r="C2556" s="4">
+        <v>4</v>
+      </c>
+      <c r="D2556" t="s" s="3">
+        <v>7</v>
+      </c>
+      <c r="E2556" t="s" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2557" ht="13.55" customHeight="1">
+      <c r="A2557" t="s" s="3">
+        <v>2395</v>
+      </c>
+      <c r="B2557" t="s" s="3">
+        <v>547</v>
+      </c>
+      <c r="C2557" s="4">
+        <v>4</v>
+      </c>
+      <c r="D2557" t="s" s="3">
+        <v>18</v>
+      </c>
+      <c r="E2557" t="s" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2558" ht="13.55" customHeight="1">
+      <c r="A2558" t="s" s="3">
+        <v>546</v>
+      </c>
+      <c r="B2558" t="s" s="3">
+        <v>547</v>
+      </c>
+      <c r="C2558" s="4">
+        <v>4</v>
+      </c>
+      <c r="D2558" t="s" s="3">
+        <v>18</v>
+      </c>
+      <c r="E2558" t="s" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2559" ht="13.55" customHeight="1">
+      <c r="A2559" t="s" s="3">
+        <v>2396</v>
+      </c>
+      <c r="B2559" t="s" s="3">
+        <v>547</v>
+      </c>
+      <c r="C2559" s="4">
+        <v>3</v>
+      </c>
+      <c r="D2559" t="s" s="3">
+        <v>18</v>
+      </c>
+      <c r="E2559" t="s" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2560" ht="13.55" customHeight="1">
+      <c r="A2560" t="s" s="3">
+        <v>2397</v>
+      </c>
+      <c r="B2560" t="s" s="3">
+        <v>547</v>
+      </c>
+      <c r="C2560" s="4">
+        <v>3</v>
+      </c>
+      <c r="D2560" t="s" s="3">
+        <v>18</v>
+      </c>
+      <c r="E2560" t="s" s="3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2561" ht="13.55" customHeight="1">
+      <c r="A2561" t="s" s="3">
+        <v>2398</v>
+      </c>
+      <c r="B2561" t="s" s="3">
+        <v>547</v>
+      </c>
+      <c r="C2561" s="4">
+        <v>2</v>
+      </c>
+      <c r="D2561" t="s" s="3">
+        <v>7</v>
+      </c>
+      <c r="E2561" t="s" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2562" ht="13.55" customHeight="1">
+      <c r="A2562" t="s" s="3">
+        <v>2399</v>
+      </c>
+      <c r="B2562" t="s" s="3">
+        <v>547</v>
+      </c>
+      <c r="C2562" s="4">
+        <v>6</v>
+      </c>
+      <c r="D2562" t="s" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E2562" t="s" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2563" ht="13.55" customHeight="1">
+      <c r="A2563" t="s" s="3">
+        <v>2401</v>
+      </c>
+      <c r="B2563" t="s" s="3">
+        <v>547</v>
+      </c>
+      <c r="C2563" s="4">
+        <v>4</v>
+      </c>
+      <c r="D2563" t="s" s="3">
+        <v>18</v>
+      </c>
+      <c r="E2563" t="s" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2564" ht="13.55" customHeight="1">
+      <c r="A2564" t="s" s="3">
+        <v>2402</v>
+      </c>
+      <c r="B2564" t="s" s="3">
+        <v>547</v>
+      </c>
+      <c r="C2564" s="4">
+        <v>4</v>
+      </c>
+      <c r="D2564" t="s" s="3">
+        <v>18</v>
+      </c>
+      <c r="E2564" t="s" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2565" ht="13.55" customHeight="1">
+      <c r="A2565" t="s" s="3">
+        <v>2403</v>
+      </c>
+      <c r="B2565" t="s" s="3">
+        <v>547</v>
+      </c>
+      <c r="C2565" s="4">
+        <v>3</v>
+      </c>
+      <c r="D2565" t="s" s="3">
+        <v>7</v>
+      </c>
+      <c r="E2565" t="s" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2566" ht="13.55" customHeight="1">
+      <c r="A2566" t="s" s="3">
+        <v>2404</v>
+      </c>
+      <c r="B2566" t="s" s="3">
+        <v>547</v>
+      </c>
+      <c r="C2566" s="4">
+        <v>5</v>
+      </c>
+      <c r="D2566" t="s" s="3">
+        <v>7</v>
+      </c>
+      <c r="E2566" t="s" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2567" ht="13.55" customHeight="1">
+      <c r="A2567" t="s" s="3">
+        <v>2405</v>
+      </c>
+      <c r="B2567" t="s" s="3">
+        <v>547</v>
+      </c>
+      <c r="C2567" s="4">
+        <v>2</v>
+      </c>
+      <c r="D2567" t="s" s="3">
+        <v>7</v>
+      </c>
+      <c r="E2567" t="s" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2568" ht="13.55" customHeight="1">
+      <c r="A2568" t="s" s="3">
+        <v>2406</v>
+      </c>
+      <c r="B2568" t="s" s="3">
+        <v>547</v>
+      </c>
+      <c r="C2568" s="4">
+        <v>4</v>
+      </c>
+      <c r="D2568" t="s" s="3">
+        <v>7</v>
+      </c>
+      <c r="E2568" t="s" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2569" ht="13.55" customHeight="1">
+      <c r="A2569" t="s" s="3">
+        <v>2407</v>
+      </c>
+      <c r="B2569" t="s" s="3">
+        <v>547</v>
+      </c>
+      <c r="C2569" s="4">
+        <v>7</v>
+      </c>
+      <c r="D2569" t="s" s="3">
+        <v>7</v>
+      </c>
+      <c r="E2569" t="s" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2570" ht="13.55" customHeight="1">
+      <c r="A2570" t="s" s="3">
+        <v>2408</v>
+      </c>
+      <c r="B2570" t="s" s="3">
+        <v>547</v>
+      </c>
+      <c r="C2570" s="4">
+        <v>5</v>
+      </c>
+      <c r="D2570" t="s" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E2570" t="s" s="3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2571" ht="13.55" customHeight="1">
+      <c r="A2571" t="s" s="3">
+        <v>2409</v>
+      </c>
+      <c r="B2571" t="s" s="3">
+        <v>547</v>
+      </c>
+      <c r="C2571" s="4">
+        <v>5</v>
+      </c>
+      <c r="D2571" t="s" s="3">
+        <v>7</v>
+      </c>
+      <c r="E2571" t="s" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2572" ht="13.55" customHeight="1">
+      <c r="A2572" t="s" s="3">
+        <v>2410</v>
+      </c>
+      <c r="B2572" t="s" s="3">
+        <v>547</v>
+      </c>
+      <c r="C2572" s="4">
+        <v>6</v>
+      </c>
+      <c r="D2572" t="s" s="3">
+        <v>7</v>
+      </c>
+      <c r="E2572" t="s" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2573" ht="13.55" customHeight="1">
+      <c r="A2573" t="s" s="3">
+        <v>548</v>
+      </c>
+      <c r="B2573" t="s" s="3">
+        <v>547</v>
+      </c>
+      <c r="C2573" s="4">
+        <v>4</v>
+      </c>
+      <c r="D2573" t="s" s="3">
+        <v>18</v>
+      </c>
+      <c r="E2573" t="s" s="3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2574" ht="13.55" customHeight="1">
+      <c r="A2574" t="s" s="3">
+        <v>2411</v>
+      </c>
+      <c r="B2574" t="s" s="3">
+        <v>547</v>
+      </c>
+      <c r="C2574" s="4">
+        <v>3</v>
+      </c>
+      <c r="D2574" t="s" s="3">
+        <v>18</v>
+      </c>
+      <c r="E2574" t="s" s="3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2575" ht="13.55" customHeight="1">
+      <c r="A2575" t="s" s="3">
+        <v>2412</v>
+      </c>
+      <c r="B2575" t="s" s="3">
+        <v>547</v>
+      </c>
+      <c r="C2575" s="4">
+        <v>6</v>
+      </c>
+      <c r="D2575" t="s" s="3">
+        <v>7</v>
+      </c>
+      <c r="E2575" t="s" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2576" ht="13.55" customHeight="1">
+      <c r="A2576" t="s" s="3">
+        <v>2413</v>
+      </c>
+      <c r="B2576" t="s" s="3">
+        <v>547</v>
+      </c>
+      <c r="C2576" s="4">
+        <v>4</v>
+      </c>
+      <c r="D2576" t="s" s="3">
+        <v>7</v>
+      </c>
+      <c r="E2576" t="s" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2577" ht="13.55" customHeight="1">
+      <c r="A2577" t="s" s="3">
+        <v>2414</v>
+      </c>
+      <c r="B2577" t="s" s="3">
+        <v>547</v>
+      </c>
+      <c r="C2577" s="4">
+        <v>4</v>
+      </c>
+      <c r="D2577" t="s" s="3">
+        <v>7</v>
+      </c>
+      <c r="E2577" t="s" s="3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2578" ht="13.55" customHeight="1">
+      <c r="A2578" t="s" s="3">
+        <v>549</v>
+      </c>
+      <c r="B2578" t="s" s="3">
+        <v>547</v>
+      </c>
+      <c r="C2578" s="4">
+        <v>7</v>
+      </c>
+      <c r="D2578" t="s" s="3">
+        <v>18</v>
+      </c>
+      <c r="E2578" t="s" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2579" ht="13.55" customHeight="1">
+      <c r="A2579" t="s" s="3">
+        <v>550</v>
+      </c>
+      <c r="B2579" t="s" s="3">
+        <v>547</v>
+      </c>
+      <c r="C2579" s="4">
+        <v>5</v>
+      </c>
+      <c r="D2579" t="s" s="3">
+        <v>7</v>
+      </c>
+      <c r="E2579" t="s" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2580" ht="13.55" customHeight="1">
+      <c r="A2580" t="s" s="3">
+        <v>2415</v>
+      </c>
+      <c r="B2580" t="s" s="3">
+        <v>547</v>
+      </c>
+      <c r="C2580" s="4">
+        <v>2</v>
+      </c>
+      <c r="D2580" t="s" s="3">
+        <v>7</v>
+      </c>
+      <c r="E2580" t="s" s="3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2581" ht="13.55" customHeight="1">
+      <c r="A2581" t="s" s="3">
+        <v>551</v>
+      </c>
+      <c r="B2581" t="s" s="3">
+        <v>547</v>
+      </c>
+      <c r="C2581" s="4">
+        <v>5</v>
+      </c>
+      <c r="D2581" t="s" s="3">
+        <v>7</v>
+      </c>
+      <c r="E2581" t="s" s="3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2582" ht="13.55" customHeight="1">
+      <c r="A2582" t="s" s="3">
+        <v>552</v>
+      </c>
+      <c r="B2582" t="s" s="3">
+        <v>547</v>
+      </c>
+      <c r="C2582" s="4">
+        <v>3</v>
+      </c>
+      <c r="D2582" t="s" s="3">
+        <v>7</v>
+      </c>
+      <c r="E2582" t="s" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2583" ht="13.55" customHeight="1">
+      <c r="A2583" t="s" s="3">
+        <v>2416</v>
+      </c>
+      <c r="B2583" t="s" s="3">
+        <v>547</v>
+      </c>
+      <c r="C2583" s="4">
+        <v>4</v>
+      </c>
+      <c r="D2583" t="s" s="3">
+        <v>7</v>
+      </c>
+      <c r="E2583" t="s" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2584" ht="13.55" customHeight="1">
+      <c r="A2584" t="s" s="3">
+        <v>2417</v>
+      </c>
+      <c r="B2584" t="s" s="3">
+        <v>547</v>
+      </c>
+      <c r="C2584" s="4">
+        <v>3</v>
+      </c>
+      <c r="D2584" t="s" s="3">
+        <v>18</v>
+      </c>
+      <c r="E2584" t="s" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2585" ht="13.55" customHeight="1">
+      <c r="A2585" t="s" s="3">
+        <v>2418</v>
+      </c>
+      <c r="B2585" t="s" s="3">
+        <v>547</v>
+      </c>
+      <c r="C2585" s="4">
+        <v>7</v>
+      </c>
+      <c r="D2585" t="s" s="3">
+        <v>7</v>
+      </c>
+      <c r="E2585" t="s" s="3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2586" ht="13.55" customHeight="1">
+      <c r="A2586" t="s" s="3">
+        <v>2419</v>
+      </c>
+      <c r="B2586" t="s" s="3">
+        <v>547</v>
+      </c>
+      <c r="C2586" s="4">
+        <v>6</v>
+      </c>
+      <c r="D2586" t="s" s="3">
+        <v>7</v>
+      </c>
+      <c r="E2586" t="s" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2587" ht="13.55" customHeight="1">
+      <c r="A2587" t="s" s="3">
+        <v>2420</v>
+      </c>
+      <c r="B2587" t="s" s="3">
+        <v>547</v>
+      </c>
+      <c r="C2587" s="4">
+        <v>4</v>
+      </c>
+      <c r="D2587" t="s" s="3">
+        <v>7</v>
+      </c>
+      <c r="E2587" t="s" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2588" ht="13.55" customHeight="1">
+      <c r="A2588" t="s" s="3">
+        <v>2421</v>
+      </c>
+      <c r="B2588" t="s" s="3">
+        <v>547</v>
+      </c>
+      <c r="C2588" s="4">
+        <v>4</v>
+      </c>
+      <c r="D2588" t="s" s="3">
+        <v>7</v>
+      </c>
+      <c r="E2588" t="s" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2589" ht="13.55" customHeight="1">
+      <c r="A2589" t="s" s="3">
+        <v>559</v>
+      </c>
+      <c r="B2589" t="s" s="3">
+        <v>547</v>
+      </c>
+      <c r="C2589" s="4">
+        <v>2</v>
+      </c>
+      <c r="D2589" t="s" s="3">
+        <v>7</v>
+      </c>
+      <c r="E2589" t="s" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2590" ht="13.55" customHeight="1">
+      <c r="A2590" t="s" s="3">
+        <v>553</v>
+      </c>
+      <c r="B2590" t="s" s="3">
+        <v>547</v>
+      </c>
+      <c r="C2590" s="4">
+        <v>4</v>
+      </c>
+      <c r="D2590" t="s" s="3">
+        <v>7</v>
+      </c>
+      <c r="E2590" t="s" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2591" ht="13.55" customHeight="1">
+      <c r="A2591" t="s" s="3">
+        <v>554</v>
+      </c>
+      <c r="B2591" t="s" s="3">
+        <v>547</v>
+      </c>
+      <c r="C2591" s="4">
+        <v>3</v>
+      </c>
+      <c r="D2591" t="s" s="3">
+        <v>18</v>
+      </c>
+      <c r="E2591" t="s" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2592" ht="13.55" customHeight="1">
+      <c r="A2592" t="s" s="3">
+        <v>2422</v>
+      </c>
+      <c r="B2592" t="s" s="3">
+        <v>547</v>
+      </c>
+      <c r="C2592" s="4">
+        <v>8</v>
+      </c>
+      <c r="D2592" t="s" s="3">
+        <v>7</v>
+      </c>
+      <c r="E2592" t="s" s="3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2593" ht="13.55" customHeight="1">
+      <c r="A2593" t="s" s="3">
+        <v>555</v>
+      </c>
+      <c r="B2593" t="s" s="3">
+        <v>547</v>
+      </c>
+      <c r="C2593" s="4">
+        <v>6</v>
+      </c>
+      <c r="D2593" t="s" s="3">
+        <v>7</v>
+      </c>
+      <c r="E2593" t="s" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2594" ht="13.55" customHeight="1">
+      <c r="A2594" t="s" s="3">
+        <v>2423</v>
+      </c>
+      <c r="B2594" t="s" s="3">
+        <v>547</v>
+      </c>
+      <c r="C2594" s="4">
+        <v>4</v>
+      </c>
+      <c r="D2594" t="s" s="3">
+        <v>7</v>
+      </c>
+      <c r="E2594" t="s" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2595" ht="13.55" customHeight="1">
+      <c r="A2595" t="s" s="3">
+        <v>2424</v>
+      </c>
+      <c r="B2595" t="s" s="3">
+        <v>547</v>
+      </c>
+      <c r="C2595" s="4">
+        <v>4</v>
+      </c>
+      <c r="D2595" t="s" s="3">
+        <v>7</v>
+      </c>
+      <c r="E2595" t="s" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2596" ht="13.55" customHeight="1">
+      <c r="A2596" t="s" s="3">
+        <v>2425</v>
+      </c>
+      <c r="B2596" t="s" s="3">
+        <v>547</v>
+      </c>
+      <c r="C2596" s="4">
+        <v>2</v>
+      </c>
+      <c r="D2596" t="s" s="3">
+        <v>7</v>
+      </c>
+      <c r="E2596" t="s" s="3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2597" ht="13.55" customHeight="1">
+      <c r="A2597" t="s" s="3">
+        <v>556</v>
+      </c>
+      <c r="B2597" t="s" s="3">
+        <v>547</v>
+      </c>
+      <c r="C2597" s="4">
+        <v>5</v>
+      </c>
+      <c r="D2597" t="s" s="3">
+        <v>7</v>
+      </c>
+      <c r="E2597" t="s" s="3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2598" ht="13.55" customHeight="1">
+      <c r="A2598" t="s" s="3">
+        <v>557</v>
+      </c>
+      <c r="B2598" t="s" s="3">
+        <v>547</v>
+      </c>
+      <c r="C2598" s="4">
+        <v>6</v>
+      </c>
+      <c r="D2598" t="s" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E2598" t="s" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2599" ht="13.55" customHeight="1">
+      <c r="A2599" t="s" s="3">
+        <v>2426</v>
+      </c>
+      <c r="B2599" t="s" s="3">
+        <v>547</v>
+      </c>
+      <c r="C2599" s="4">
+        <v>5</v>
+      </c>
+      <c r="D2599" t="s" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E2599" t="s" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2600" ht="13.55" customHeight="1">
+      <c r="A2600" t="s" s="3">
+        <v>1112</v>
+      </c>
+      <c r="B2600" t="s" s="3">
+        <v>547</v>
+      </c>
+      <c r="C2600" s="4">
+        <v>4</v>
+      </c>
+      <c r="D2600" t="s" s="3">
+        <v>7</v>
+      </c>
+      <c r="E2600" t="s" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2601" ht="13.55" customHeight="1">
+      <c r="A2601" t="s" s="3">
+        <v>558</v>
+      </c>
+      <c r="B2601" t="s" s="3">
+        <v>547</v>
+      </c>
+      <c r="C2601" s="4">
+        <v>5</v>
+      </c>
+      <c r="D2601" t="s" s="3">
+        <v>7</v>
+      </c>
+      <c r="E2601" t="s" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2602" ht="13.55" customHeight="1">
+      <c r="A2602" t="s" s="3">
+        <v>2427</v>
+      </c>
+      <c r="B2602" t="s" s="3">
+        <v>547</v>
+      </c>
+      <c r="C2602" s="4">
+        <v>6</v>
+      </c>
+      <c r="D2602" t="s" s="3">
+        <v>7</v>
+      </c>
+      <c r="E2602" t="s" s="3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2603" ht="13.55" customHeight="1">
+      <c r="A2603" t="s" s="3">
+        <v>2428</v>
+      </c>
+      <c r="B2603" t="s" s="3">
+        <v>547</v>
+      </c>
+      <c r="C2603" s="4">
+        <v>5</v>
+      </c>
+      <c r="D2603" t="s" s="3">
+        <v>7</v>
+      </c>
+      <c r="E2603" t="s" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2604" ht="13.55" customHeight="1">
+      <c r="A2604" t="s" s="3">
+        <v>2429</v>
+      </c>
+      <c r="B2604" t="s" s="3">
+        <v>547</v>
+      </c>
+      <c r="C2604" s="4">
+        <v>3</v>
+      </c>
+      <c r="D2604" t="s" s="3">
+        <v>7</v>
+      </c>
+      <c r="E2604" t="s" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2605" ht="13.55" customHeight="1">
+      <c r="A2605" t="s" s="3">
+        <v>2430</v>
+      </c>
+      <c r="B2605" t="s" s="3">
+        <v>547</v>
+      </c>
+      <c r="C2605" s="4">
+        <v>1</v>
+      </c>
+      <c r="D2605" t="s" s="3">
+        <v>7</v>
+      </c>
+      <c r="E2605" t="s" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2606" ht="13.55" customHeight="1">
+      <c r="A2606" t="s" s="3">
+        <v>2431</v>
+      </c>
+      <c r="B2606" t="s" s="3">
+        <v>547</v>
+      </c>
+      <c r="C2606" s="4">
+        <v>7</v>
+      </c>
+      <c r="D2606" t="s" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E2606" t="s" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2607" ht="13.55" customHeight="1">
+      <c r="A2607" t="s" s="3">
+        <v>560</v>
+      </c>
+      <c r="B2607" t="s" s="3">
+        <v>547</v>
+      </c>
+      <c r="C2607" s="4">
+        <v>3</v>
+      </c>
+      <c r="D2607" t="s" s="3">
+        <v>7</v>
+      </c>
+      <c r="E2607" t="s" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2608" ht="13.55" customHeight="1">
+      <c r="A2608" t="s" s="3">
+        <v>2432</v>
+      </c>
+      <c r="B2608" t="s" s="3">
+        <v>547</v>
+      </c>
+      <c r="C2608" s="4">
+        <v>4</v>
+      </c>
+      <c r="D2608" t="s" s="3">
+        <v>18</v>
+      </c>
+      <c r="E2608" t="s" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2609" ht="13.55" customHeight="1">
+      <c r="A2609" t="s" s="3">
+        <v>2433</v>
+      </c>
+      <c r="B2609" t="s" s="3">
+        <v>547</v>
+      </c>
+      <c r="C2609" s="4">
+        <v>3</v>
+      </c>
+      <c r="D2609" t="s" s="3">
+        <v>18</v>
+      </c>
+      <c r="E2609" t="s" s="3">
         <v>8</v>
       </c>
     </row>

--- a/carddata/Duel_Masters_Card_Database.xlsx
+++ b/carddata/Duel_Masters_Card_Database.xlsx
@@ -7345,12 +7345,18 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="9"/>
+        <bgColor auto="1"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -7363,16 +7369,16 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </left>
       <right style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </right>
       <top style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </top>
       <bottom style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </bottom>
       <diagonal/>
     </border>
@@ -7389,16 +7395,16 @@
     <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="3" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
@@ -7418,6 +7424,7 @@
       <rgbColor rgb="ffff00ff"/>
       <rgbColor rgb="ff00ffff"/>
       <rgbColor rgb="ff000000"/>
+      <rgbColor rgb="ffffffff"/>
       <rgbColor rgb="ffaaaaaa"/>
     </indexedColors>
   </colors>
@@ -7569,9 +7576,9 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="20000" dir="5400000">
+            <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="23000" dir="5400000">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
@@ -7651,7 +7658,7 @@
         </a:effectLst>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr" upright="0">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -7678,10 +7685,10 @@
             </a:solidFill>
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="Calibri"/>
-            <a:ea typeface="Calibri"/>
-            <a:cs typeface="Calibri"/>
-            <a:sym typeface="Calibri"/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+            <a:sym typeface="Helvetica Neue"/>
           </a:defRPr>
         </a:defPPr>
         <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
@@ -7928,9 +7935,9 @@
           <a:round/>
         </a:ln>
         <a:effectLst>
-          <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="20000" dir="5400000">
+          <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="23000" dir="5400000">
             <a:srgbClr val="000000">
-              <a:alpha val="38000"/>
+              <a:alpha val="35000"/>
             </a:srgbClr>
           </a:outerShdw>
         </a:effectLst>
@@ -8208,7 +8215,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -8235,10 +8242,10 @@
             </a:solidFill>
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="Calibri"/>
-            <a:ea typeface="Calibri"/>
-            <a:cs typeface="Calibri"/>
-            <a:sym typeface="Calibri"/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+            <a:sym typeface="Helvetica Neue"/>
           </a:defRPr>
         </a:defPPr>
         <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
@@ -16966,7 +16973,7 @@
         <v>18</v>
       </c>
       <c r="E499" t="s" s="3">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="500" ht="13.55" customHeight="1">
@@ -17493,7 +17500,7 @@
         <v>18</v>
       </c>
       <c r="E530" t="s" s="3">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="531" ht="13.55" customHeight="1">
@@ -19017,7 +19024,7 @@
         <v>18</v>
       </c>
       <c r="E620" t="s" s="3">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="621" ht="13.55" customHeight="1">
@@ -21645,7 +21652,7 @@
         <v>18</v>
       </c>
       <c r="E778" t="s" s="3">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="779" ht="13.55" customHeight="1">
@@ -34297,7 +34304,7 @@
         <v>18</v>
       </c>
       <c r="E1532" t="s" s="3">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1533" ht="13.55" customHeight="1">
@@ -36870,7 +36877,7 @@
         <v>18</v>
       </c>
       <c r="E1687" t="s" s="3">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1688" ht="13.55" customHeight="1">
@@ -42047,7 +42054,7 @@
         <v>18</v>
       </c>
       <c r="E2012" t="s" s="3">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2013" ht="13.55" customHeight="1">
@@ -42098,7 +42105,7 @@
         <v>18</v>
       </c>
       <c r="E2015" t="s" s="3">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2016" ht="13.55" customHeight="1">

--- a/carddata/Duel_Masters_Card_Database.xlsx
+++ b/carddata/Duel_Masters_Card_Database.xlsx
@@ -41828,7 +41828,9 @@
       <c r="B1997" t="s" s="3">
         <v>1790</v>
       </c>
-      <c r="C1997" s="5"/>
+      <c r="C1997" s="4">
+        <v>1</v>
+      </c>
       <c r="D1997" t="s" s="3">
         <v>7</v>
       </c>
@@ -41846,7 +41848,9 @@
       <c r="C1998" s="4">
         <v>8</v>
       </c>
-      <c r="D1998" s="5"/>
+      <c r="D1998" t="s" s="3">
+        <v>1113</v>
+      </c>
       <c r="E1998" t="s" s="3">
         <v>35</v>
       </c>
@@ -41946,7 +41950,9 @@
       <c r="C2004" s="4">
         <v>7</v>
       </c>
-      <c r="D2004" s="5"/>
+      <c r="D2004" t="s" s="3">
+        <v>1113</v>
+      </c>
       <c r="E2004" t="s" s="3">
         <v>35</v>
       </c>
@@ -41995,7 +42001,9 @@
       <c r="C2007" s="4">
         <v>7</v>
       </c>
-      <c r="D2007" s="5"/>
+      <c r="D2007" t="s" s="3">
+        <v>7</v>
+      </c>
       <c r="E2007" t="s" s="3">
         <v>35</v>
       </c>

--- a/carddata/Duel_Masters_Card_Database.xlsx
+++ b/carddata/Duel_Masters_Card_Database.xlsx
@@ -8778,23 +8778,23 @@
   <dimension ref="A1:R2610"/>
   <sheetFormatPr defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="29.1328" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.22656" style="1" customWidth="1"/>
+    <col min="1" max="1" width="29.1719" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.17188" style="1" customWidth="1"/>
     <col min="3" max="3" width="7.17188" style="1" customWidth="1"/>
     <col min="4" max="4" width="14" style="1" customWidth="1"/>
     <col min="5" max="5" width="15.1719" style="1" customWidth="1"/>
     <col min="6" max="6" width="18" style="1" customWidth="1"/>
-    <col min="7" max="7" width="16.4062" style="1" customWidth="1"/>
-    <col min="8" max="8" width="11.875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5781" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.44531" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.5" style="1" customWidth="1"/>
+    <col min="8" max="8" width="11.8516" style="1" customWidth="1"/>
+    <col min="9" max="9" width="12.6719" style="1" customWidth="1"/>
+    <col min="10" max="10" width="8.5" style="1" customWidth="1"/>
     <col min="11" max="11" width="12.5" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.90625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="9.85156" style="1" customWidth="1"/>
     <col min="13" max="13" width="9.17188" style="1" customWidth="1"/>
     <col min="14" max="14" width="9.67188" style="1" customWidth="1"/>
     <col min="15" max="15" width="12.8516" style="1" customWidth="1"/>
-    <col min="16" max="16" width="14.8438" style="1" customWidth="1"/>
-    <col min="17" max="18" width="28.2109" style="1" customWidth="1"/>
+    <col min="16" max="16" width="14.8516" style="1" customWidth="1"/>
+    <col min="17" max="18" width="28.1719" style="1" customWidth="1"/>
     <col min="19" max="16384" width="8.85156" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -16001,7 +16001,7 @@
         <v>6</v>
       </c>
       <c r="D232" t="s" s="3">
-        <v>20</v>
+        <v>182</v>
       </c>
       <c r="E232" t="s" s="3">
         <v>63</v>

--- a/carddata/Duel_Masters_Card_Database.xlsx
+++ b/carddata/Duel_Masters_Card_Database.xlsx
@@ -20455,7 +20455,9 @@
       <c r="F376" s="3"/>
       <c r="G376" s="3"/>
       <c r="H376" s="3"/>
-      <c r="I376" s="3"/>
+      <c r="I376" t="s" s="3">
+        <v>43</v>
+      </c>
       <c r="J376" s="3"/>
       <c r="K376" s="3"/>
       <c r="L376" s="3"/>
